--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -17350,10 +17350,35 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>25/F</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+$3,228万
+$25,300/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>25&amp;26/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>A | 2780呎 (4+房)
 暂无价格
@@ -17361,33 +17386,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-$3,228万
-$25,300/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
@@ -18148,10 +18148,35 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>25/F</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>25&amp;26/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>A | 2829呎 (4+房)
 暂无价格
@@ -18159,33 +18184,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
@@ -18960,10 +18960,37 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>25/F</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 768呎 (3房)
+$1,976万
+$25,736/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>25&amp;26/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>A | 2599呎 (4+房)
 暂无价格
@@ -18971,7 +18998,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>B | 2876呎 (4+房)
 暂无价格
@@ -18979,37 +19006,10 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
       <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>F | 768呎 (3房)
-$1,976万
-$25,736/呎
-(在售)</t>
-        </is>
-      </c>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -20597,11 +20597,27 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>25/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>25&amp;26/F</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>B | 2493呎 (4+房)
 暂无价格
@@ -20609,22 +20625,6 @@
 (待售)</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -8,12 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座 销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -116,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16704,4278 +16557,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23&amp;25/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2922呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 3165呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1992呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1930呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1934呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 2020呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>47 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-$3,228万
-$25,300/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1711呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1711呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-$3,831万
-$30,020/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-$3,690万
-$28,298/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1625呎 (4+房)
-$5,165万
-$31,782/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1625呎 (4+房)
-$4,962万
-$30,535/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1625呎 (4+房)
-$4,962万
-$30,535/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,789万
-$22,745/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-$2,875万
-$22,050/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1625呎 (4+房)
-$4,791万
-$29,482/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1276呎 (3房)
-$3,549万
-$27,813/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 1304呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1711呎 (4+房)
-$4,600万
-$26,885/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$3,061万
-$24,969/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1254呎 (3房)
-$2,960万
-$23,605/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$2,145万
-$22,700/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$3,015万
-$24,594/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,591万
-$20,695/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,643万
-$22,700/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$2,060万
-$21,800/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,942万
-$24,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 1302呎 (3房)
-$3,204万
-$24,609/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,578万
-$21,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,975万
-$20,900/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,897万
-$23,626/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 1302呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,513万
-$20,900/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,909万
-$20,200/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,475万
-$20,191/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,708万
-$21,631/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,548万
-$21,380/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,843万
-$19,500/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,419万
-$19,733/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,331万
-$18,615/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,419万
-$19,600/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,777万
-$18,800/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,348万
-$19,150/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,292万
-$18,303/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,361万
-$18,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,692万
-$17,900/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,549万
-$20,789/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,252万
-$17,991/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,300万
-$17,950/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,635万
-$17,300/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,463万
-$20,087/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,213万
-$17,679/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,281万
-$17,700/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 945呎 (3房)
-$1,577万
-$16,688/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1226呎 (3房)
-$2,450万
-$19,983/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 1252呎 (3房)
-$2,252万
-$17,991/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 724呎 (2房)
-$1,339万
-$18,499/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1532呎 (4+房)
-$3,964万
-$25,873/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 1210呎 (3房)
-$2,884万
-$23,836/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 1254呎 (3房)
-$2,478万
-$19,758/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1760呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 933呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 782呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1669呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1209呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 1198呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>69 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>35 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>F | 768呎 (3房)
-$1,996万
-$25,993/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 768呎 (3房)
-$1,976万
-$25,736/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1865呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>F | 768呎 (3房)
-$1,957万
-$25,481/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1865呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 768呎 (3房)
-$1,821万
-$23,715/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1865呎 (4+房)
-$6,600万
-$35,389/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,803万
-$23,450/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1788呎 (4+房)
-$6,900万
-$38,593/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,785万
-$23,217/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1788呎 (4+房)
-$5,908万
-$33,044/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,682万
-$21,872/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1788呎 (4+房)
-$6,051万
-$33,841/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-$5,883万
-$31,695/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr"/>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,628万
-$21,172/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1788呎 (4+房)
-$5,456万
-$30,514/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1856呎 (4+房)
-$5,603万
-$30,186/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,574万
-$20,473/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$2,289万
-$23,239/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 725呎 (2房)
-$1,579万
-$21,775/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 961呎 (3房)
-$2,704万
-$28,133/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 748呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 769呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,528万
-$19,874/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$2,090万
-$21,216/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 725呎 (2房)
-$1,548万
-$21,348/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 961呎 (3房)
-$2,820万
-$29,342/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 748呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 769呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,490万
-$19,375/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$2,009万
-$20,400/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 725呎 (2房)
-$1,517万
-$20,929/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 961呎 (3房)
-$2,764万
-$28,767/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 748呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 769呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,432万
-$18,626/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,931万
-$19,600/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 725呎 (2房)
-$1,467万
-$20,228/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 961呎 (3房)
-$2,690万
-$27,996/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 748呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 769呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 769呎 (3房)
-$1,448万
-$18,828/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,862万
-$18,900/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 727呎 (2房)
-$1,423万
-$19,573/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr"/>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,807万
-$18,350/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 729呎 (2房)
-$1,383万
-$18,974/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr"/>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,753万
-$17,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 729呎 (2房)
-$1,416万
-$19,417/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr"/>
-      <c r="F22" s="17" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,714万
-$17,400/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 729呎 (2房)
-$1,281万
-$17,576/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr"/>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 985呎 (3房)
-$1,684万
-$17,100/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 729呎 (2房)
-$1,252万
-$17,176/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-      <c r="F24" s="17" t="inlineStr"/>
-      <c r="G24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1640呎 (3房)
-$4,380万
-$26,707/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr"/>
-      <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>66 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,586万
-$20,623/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,504万
-$21,126/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-$4,811万
-$30,936/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,733万
-$30,936/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,563万
-$20,324/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,478万
-$20,758/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-$4,679万
-$30,092/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,635万
-$30,293/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,540万
-$20,024/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,452万
-$20,390/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,536万
-$29,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,517万
-$19,724/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,356万
-$19,050/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,494万
-$19,425/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,339万
-$18,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,810万
-$25,432/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,471万
-$19,125/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,321万
-$18,550/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,452万
-$18,875/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,296万
-$18,200/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,432万
-$18,626/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,278万
-$17,950/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-$3,703万
-$23,814/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,101万
-$26,807/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,398万
-$18,176/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,257万
-$17,650/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,370万
-$22,497/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,080万
-$26,669/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,379万
-$17,927/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,242万
-$17,450/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,314万
-$22,121/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$4,021万
-$26,281/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 768呎 (3房)
-$1,432万
-$18,642/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,228万
-$17,250/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,234万
-$21,591/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1473呎 (4+房)
-$3,244万
-$22,020/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,340万
-$17,427/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,214万
-$17,050/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,380万
-$22,562/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1473呎 (4+房)
-$3,583万
-$24,327/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,321万
-$17,178/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,200万
-$16,850/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,140万
-$20,960/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1530呎 (4+房)
-$3,766万
-$24,612/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 769呎 (3房)
-$1,297万
-$16,866/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 712呎 (2房)
-$1,139万
-$15,998/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,079万
-$20,553/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1478呎 (4+房)
-$3,343万
-$22,621/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,110万
-$20,761/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1478呎 (4+房)
-$2,993万
-$20,252/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr"/>
-      <c r="E21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,063万
-$20,450/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1535呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1498呎 (4+房)
-$3,126万
-$20,865/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-$2,930万
-$19,691/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1545呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Beacon Peak 第1期 - 7座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25&amp;26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1552呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1539呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1462呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1319呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +158,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +239,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +675,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -16557,4 +16758,4278 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2922呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 3165呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1992呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1930呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1934呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 2020呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+$3228万
+$25,300/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1711呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1711呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+$3831万
+$30,020/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+$3690万
+$28,298/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1625呎 (4+房)
+$5165万
+$31,782/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1625呎 (4+房)
+$4962万
+$30,535/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1625呎 (4+房)
+$4962万
+$30,535/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2789万
+$22,745/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+$2875万
+$22,050/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1625呎 (4+房)
+$4791万
+$29,482/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1276呎 (3房)
+$3549万
+$27,813/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 1304呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1711呎 (4+房)
+$4600万
+$26,885/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$3061万
+$24,969/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1254呎 (3房)
+$2960万
+$23,605/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$2145万
+$22,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$3015万
+$24,594/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2591万
+$20,695/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1643万
+$22,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$2060万
+$21,800/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2942万
+$24,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 1302呎 (3房)
+$3204万
+$24,609/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1578万
+$21,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1975万
+$20,900/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2897万
+$23,626/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 1302呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1513万
+$20,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1909万
+$20,200/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2475万
+$20,191/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2708万
+$21,631/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1548万
+$21,380/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1843万
+$19,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2419万
+$19,733/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2331万
+$18,615/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1419万
+$19,600/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1777万
+$18,800/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2348万
+$19,150/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2292万
+$18,303/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1361万
+$18,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1692万
+$17,900/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2549万
+$20,789/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2252万
+$17,991/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1300万
+$17,950/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1635万
+$17,300/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2463万
+$20,087/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2213万
+$17,679/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1281万
+$17,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 945呎 (3房)
+$1577万
+$16,688/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1226呎 (3房)
+$2450万
+$19,983/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 1252呎 (3房)
+$2252万
+$17,991/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 724呎 (2房)
+$1339万
+$18,499/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1532呎 (4+房)
+$3964万
+$25,873/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1210呎 (3房)
+$2884万
+$23,836/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 1254呎 (3房)
+$2478万
+$19,758/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1760呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 933呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 782呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1669呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1209呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 1198呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>F | 768呎 (3房)
+$1996万
+$25,993/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>F | 768呎 (3房)
+$1976万
+$25,736/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1865呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>F | 768呎 (3房)
+$1957万
+$25,481/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1865呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 768呎 (3房)
+$1821万
+$23,715/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1865呎 (4+房)
+$6600万
+$35,389/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1803万
+$23,450/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1788呎 (4+房)
+$6900万
+$38,593/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1785万
+$23,217/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1788呎 (4+房)
+$5908万
+$33,044/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1682万
+$21,872/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1788呎 (4+房)
+$6051万
+$33,841/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+$5883万
+$31,695/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1628万
+$21,172/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1788呎 (4+房)
+$5456万
+$30,514/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1856呎 (4+房)
+$5603万
+$30,186/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
+      <c r="E14" s="21" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1574万
+$20,473/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$2289万
+$23,239/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 725呎 (2房)
+$1579万
+$21,775/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 961呎 (3房)
+$2704万
+$28,133/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 748呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 769呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1528万
+$19,874/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$2090万
+$21,216/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 725呎 (2房)
+$1548万
+$21,348/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>C | 961呎 (3房)
+$2820万
+$29,342/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 748呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 769呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1490万
+$19,375/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$2009万
+$20,400/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 725呎 (2房)
+$1517万
+$20,929/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>C | 961呎 (3房)
+$2764万
+$28,767/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 748呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 769呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1432万
+$18,626/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1931万
+$19,600/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 725呎 (2房)
+$1467万
+$20,228/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>C | 961呎 (3房)
+$2690万
+$27,996/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 748呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 769呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 769呎 (3房)
+$1448万
+$18,828/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1862万
+$18,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 727呎 (2房)
+$1423万
+$19,573/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr"/>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1807万
+$18,350/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 729呎 (2房)
+$1383万
+$18,974/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
+      <c r="E20" s="21" t="inlineStr"/>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1753万
+$17,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 729呎 (2房)
+$1416万
+$19,417/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1714万
+$17,400/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 729呎 (2房)
+$1281万
+$17,576/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr"/>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 985呎 (3房)
+$1684万
+$17,100/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 729呎 (2房)
+$1252万
+$17,176/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr"/>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1640呎 (3房)
+$4380万
+$26,707/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr"/>
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr"/>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1586万
+$20,623/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1504万
+$21,126/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+$4811万
+$30,936/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4733万
+$30,936/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1563万
+$20,324/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1478万
+$20,758/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+$4679万
+$30,092/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4635万
+$30,293/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1540万
+$20,024/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1452万
+$20,390/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4536万
+$29,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1517万
+$19,724/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1356万
+$19,050/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1494万
+$19,425/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1339万
+$18,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3810万
+$25,432/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1471万
+$19,125/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1321万
+$18,550/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1452万
+$18,875/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1296万
+$18,200/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1432万
+$18,626/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1278万
+$17,950/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+$3703万
+$23,814/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4101万
+$26,807/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1398万
+$18,176/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1257万
+$17,650/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3370万
+$22,497/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4080万
+$26,669/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1379万
+$17,927/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1242万
+$17,450/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3314万
+$22,121/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$4021万
+$26,281/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 768呎 (3房)
+$1432万
+$18,642/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1228万
+$17,250/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3234万
+$21,591/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1473呎 (4+房)
+$3244万
+$22,020/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1340万
+$17,427/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1214万
+$17,050/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3380万
+$22,562/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1473呎 (4+房)
+$3583万
+$24,327/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1321万
+$17,178/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1200万
+$16,850/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3140万
+$20,960/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1530呎 (4+房)
+$3766万
+$24,612/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 769呎 (3房)
+$1297万
+$16,866/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 712呎 (2房)
+$1139万
+$15,998/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3079万
+$20,553/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1478呎 (4+房)
+$3343万
+$22,621/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3110万
+$20,761/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1478呎 (4+房)
+$2993万
+$20,252/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
+      <c r="E20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3063万
+$20,450/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1535呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1498呎 (4+房)
+$3126万
+$20,865/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+$2930万
+$19,691/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1545呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>7座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1552呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1539呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1462呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1319呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -675,7 +675,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17404,29 +17404,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -17434,7 +17416,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -17442,6 +17424,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -18202,44 +18202,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -19014,41 +19014,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -19056,7 +19029,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -19064,6 +19037,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -20651,34 +20651,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J334"/>
+  <dimension ref="A1:N334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -678,6 +678,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -735,6 +739,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -785,6 +809,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -835,6 +879,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -885,6 +949,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -935,6 +1019,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -985,6 +1089,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1035,6 +1159,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1085,6 +1229,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1135,6 +1299,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1185,6 +1369,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1235,6 +1439,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1285,6 +1509,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1335,6 +1579,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1385,6 +1649,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1435,6 +1719,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1485,6 +1789,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1535,6 +1859,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1585,6 +1929,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1635,6 +1999,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1685,6 +2069,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1735,6 +2139,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1785,6 +2209,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1835,6 +2279,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1885,6 +2349,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1935,6 +2419,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1985,6 +2489,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2035,6 +2559,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2085,6 +2629,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2135,6 +2699,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2185,6 +2769,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2235,6 +2839,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2285,6 +2909,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2335,6 +2979,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2385,6 +3049,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2435,6 +3119,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2485,6 +3189,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2535,6 +3259,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2585,6 +3329,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2631,6 +3395,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>32282800</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>25300</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2681,6 +3461,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2731,6 +3531,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2781,6 +3601,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2831,6 +3671,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2877,6 +3737,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>34686000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>26600</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2923,6 +3799,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>36006982</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>28219</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2973,6 +3865,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3023,6 +3935,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3073,6 +4005,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3119,6 +4071,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>51645600</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>31782</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3169,6 +4137,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3219,6 +4207,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3265,6 +4273,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>49619000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>30535</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3311,6 +4335,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>28753200</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>22050</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3357,6 +4397,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>27885704</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>22745</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3403,6 +4459,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>49619000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>30535</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3453,6 +4525,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3499,6 +4591,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>33360036</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>26144</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3545,6 +4653,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>47908000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>29482</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3591,6 +4715,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>29600800</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>23605</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3637,6 +4777,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>30612000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>24969</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3683,6 +4839,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>26885</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3729,6 +4901,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>16434800</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>22700</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3775,6 +4963,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>25909800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>20695</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3821,6 +5025,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>30152000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>24594</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3867,6 +5087,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>21451500</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22700</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3913,6 +5149,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>15783200</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>21800</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3959,6 +5211,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>30119010</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>23133</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4005,6 +5273,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>29424560</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4051,6 +5335,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>20601000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>21800</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4097,6 +5397,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>15131600</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>20900</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4147,6 +5463,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4193,6 +5529,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>28965200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>23626</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4239,6 +5591,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>19750500</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>20900</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4285,6 +5653,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>15478900</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>21380</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4331,6 +5715,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>27081600</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>21631</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4377,6 +5777,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>24754400</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>20191</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4423,6 +5839,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>19089000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>20200</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4469,6 +5901,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>14190400</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>19600</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4515,6 +5963,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>23305800</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>18615</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4561,6 +6025,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>24192960</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>19733</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4607,6 +6087,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>18427500</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>19500</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4653,6 +6149,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>13611200</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4699,6 +6211,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>22915200</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>18303</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4745,6 +6273,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>23478400</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>19150</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4791,6 +6335,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>17766000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4837,6 +6397,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>12995800</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>17950</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4883,6 +6459,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>22524600</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>17991</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4929,6 +6521,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>25487000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>20789</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4975,6 +6583,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>16915500</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>17900</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5021,6 +6645,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>12814800</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>17700</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5067,6 +6707,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>22134000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>17679</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5113,6 +6769,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>24626800</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>20087</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5159,6 +6831,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>16348500</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>17300</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5205,6 +6893,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>13393000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>18499</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5251,6 +6955,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>22524600</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>17991</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5297,6 +7017,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>24499200</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>19983</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5343,6 +7079,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>15770200</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>16688</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5389,6 +7141,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>24776000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>19758</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5435,6 +7203,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>28841400</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>23836</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5481,6 +7265,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>39637000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>25873</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5531,6 +7331,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5581,6 +7401,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5631,6 +7471,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5681,6 +7541,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5731,6 +7611,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5781,6 +7681,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5831,6 +7751,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5881,6 +7821,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5931,6 +7891,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5981,6 +7961,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6031,6 +8031,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6081,6 +8101,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6131,6 +8171,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6181,6 +8241,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6231,6 +8311,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6281,6 +8381,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6331,6 +8451,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6381,6 +8521,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6431,6 +8591,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6481,6 +8661,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6531,6 +8731,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6581,6 +8801,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6631,6 +8871,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6681,6 +8941,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6731,6 +9011,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6781,6 +9081,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6831,6 +9151,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6881,6 +9221,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6931,6 +9291,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6981,6 +9361,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7031,6 +9431,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7081,6 +9501,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7131,6 +9571,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7181,6 +9641,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7231,6 +9711,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7281,6 +9781,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7331,6 +9851,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7381,6 +9921,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7431,6 +9991,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7481,6 +10061,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7531,6 +10131,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7581,6 +10201,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7631,6 +10271,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7681,6 +10341,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7731,6 +10411,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7781,6 +10481,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7831,6 +10551,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7881,6 +10621,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7931,6 +10691,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7981,6 +10761,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8031,6 +10831,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8081,6 +10901,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8131,6 +10971,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8181,6 +11041,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8231,6 +11111,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8281,6 +11181,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8331,6 +11251,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8381,6 +11321,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8431,6 +11391,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8481,6 +11461,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8531,6 +11531,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8581,6 +11601,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8631,6 +11671,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8681,6 +11741,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8731,6 +11811,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8777,6 +11877,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>18765032</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>24434</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8827,6 +11943,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8873,6 +12009,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>18579006</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>24191</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8923,6 +12075,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8973,6 +12145,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9023,6 +12215,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9069,6 +12281,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>18394954</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>23952</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9119,6 +12347,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9169,6 +12417,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9219,6 +12487,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9265,6 +12553,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>18213000</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>23715</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9315,6 +12619,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9365,6 +12689,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9415,6 +12759,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9461,6 +12825,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>18033000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>23450</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9511,6 +12891,26 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9561,6 +12961,26 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9587,7 +13007,7 @@
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>1865</v>
+        <v>1788</v>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
@@ -9603,9 +13023,25 @@
         <v>66000000</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>35389</v>
+        <v>36913</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>36913</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9653,6 +13089,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>17854000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>23217</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9703,6 +13155,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9753,6 +13225,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9799,6 +13291,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>69005000</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>38593</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9845,6 +13353,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>16819200</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21872</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9895,6 +13419,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9945,6 +13489,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9991,6 +13555,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>59083200</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>33044</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10037,6 +13617,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>16281600</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>21172</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10087,6 +13683,26 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10133,6 +13749,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>55297004</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>29794</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10179,6 +13811,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>60506900</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>33841</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10225,6 +13873,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>15744000</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>20473</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10275,6 +13939,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10321,6 +14005,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>52663970</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>28375</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10367,6 +14067,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>54559000</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>30514</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10413,6 +14129,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>15283200</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>19874</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10463,6 +14195,26 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10513,6 +14265,26 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10559,6 +14331,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>27036000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>28133</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10605,6 +14393,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>15787000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21775</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10651,6 +14455,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>22890100</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>23239</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10697,6 +14517,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>14899200</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>19375</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10747,6 +14583,26 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10797,6 +14653,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10843,6 +14719,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>26506026</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>27582</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10889,6 +14781,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>15477000</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>21348</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10935,6 +14843,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>20898000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>21216</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10981,6 +14905,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>14323200</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>18626</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11031,6 +14971,26 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11081,6 +15041,26 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11127,6 +15107,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>25986018</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>27041</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11173,6 +15169,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>15173400</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>20929</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11219,6 +15231,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>20094000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>20400</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11265,6 +15293,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>14478500</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>18828</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11315,6 +15359,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11365,6 +15429,26 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11411,6 +15495,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>25290042</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>26316</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11457,6 +15557,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>14665200</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>20228</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11503,6 +15619,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>19306000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>19600</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11549,6 +15681,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>14229600</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>19573</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11595,6 +15743,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>18616500</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>18900</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11641,6 +15805,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>13832000</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>18974</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11687,6 +15867,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>18074800</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>18350</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11733,6 +15929,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>14155000</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>19417</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11779,6 +15991,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>17533000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>17800</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11825,6 +16053,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>12812800</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>17576</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11871,6 +16115,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>17139000</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11917,6 +16177,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>12521600</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>17176</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11963,6 +16239,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>16843500</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>17100</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12009,6 +16301,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>43800000</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>26707</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12055,6 +16363,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>15042000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>21126</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12101,6 +16425,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>15859200</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>20623</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12151,6 +16491,26 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12201,6 +16561,26 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12247,6 +16627,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>14780000</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>20758</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12293,6 +16689,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>15628800</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>20324</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12339,6 +16751,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>44491986</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>29080</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12385,6 +16813,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>45218982</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>29080</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12431,6 +16875,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>14518000</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>20390</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12477,6 +16937,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>15398400</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>20024</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12523,6 +16999,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>43567026</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>28475</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12569,6 +17061,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>43985044</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>28286</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12615,6 +17123,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>13563600</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>19050</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12661,6 +17185,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>15168000</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>19724</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12707,6 +17247,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>42641972</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>27871</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12757,6 +17313,26 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12803,6 +17379,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>13385600</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12849,6 +17441,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>14937600</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>19425</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12899,6 +17507,26 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12949,6 +17577,26 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12995,6 +17643,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>13207600</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>18550</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13041,6 +17705,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>14707200</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>19125</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13091,6 +17771,26 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13137,6 +17837,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>38097500</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>25432</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13183,6 +17899,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>12958400</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>18200</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13229,6 +17961,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>14515200</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>18875</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13279,6 +18027,26 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13329,6 +18097,26 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13375,6 +18163,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>12780400</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>17950</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13421,6 +18225,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>14323200</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>18626</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13471,6 +18291,26 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13521,6 +18361,26 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13567,6 +18427,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>12566800</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>17650</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13613,6 +18489,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>13977600</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>18176</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13659,6 +18551,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>38554006</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>25199</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13705,6 +18613,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>37030800</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>23814</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13751,6 +18675,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>12424400</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>17450</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13797,6 +18737,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>13785600</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>17927</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13843,6 +18799,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>38356042</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>25069</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13889,6 +18861,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>33700000</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>22497</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13935,6 +18923,22 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>12282000</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>17250</v>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13981,6 +18985,22 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>14316700</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>18642</v>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14027,6 +19047,22 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>37797964</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>24705</v>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14073,6 +19109,22 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>33138000</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>22121</v>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14119,6 +19171,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>12139600</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>17050</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14165,6 +19233,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>13401600</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>17427</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14211,6 +19295,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>32436000</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>22020</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14257,6 +19357,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>32344000</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>21591</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14303,6 +19419,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>11997200</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>16850</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14349,6 +19481,22 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>13209600</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>17178</v>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14395,6 +19543,22 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>35834130</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>24327</v>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14441,6 +19605,22 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>33797900</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>22562</v>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14487,6 +19667,22 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>11390600</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>15998</v>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14533,6 +19729,22 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>12970000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>16866</v>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14579,6 +19791,22 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>35397016</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>23135</v>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14625,6 +19853,22 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>31398000</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>20960</v>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14671,6 +19915,22 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>33434000</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>22621</v>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14717,6 +19977,22 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>30789000</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>20553</v>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14763,6 +20039,22 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>29932500</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>20252</v>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14809,6 +20101,22 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="5" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>20761</v>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14859,6 +20167,26 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14905,6 +20233,22 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>30633500</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>20450</v>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14951,6 +20295,22 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" s="5" t="n">
+        <v>29300000</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>19691</v>
+      </c>
+      <c r="M298" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14997,6 +20357,22 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" s="5" t="n">
+        <v>31255500</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>20865</v>
+      </c>
+      <c r="M299" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15047,6 +20423,26 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M300" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15097,6 +20493,26 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L301" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M301" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15147,6 +20563,26 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L302" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M302" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15197,6 +20633,26 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15247,6 +20703,26 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M304" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15297,6 +20773,26 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M305" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15347,6 +20843,26 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L306" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M306" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15397,6 +20913,26 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M307" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15447,6 +20983,26 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L308" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M308" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15497,6 +21053,26 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M309" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15547,6 +21123,26 @@
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L310" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M310" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15597,6 +21193,26 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M311" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15647,6 +21263,26 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L312" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M312" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15697,6 +21333,26 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L313" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M313" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15747,6 +21403,26 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M314" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15797,6 +21473,26 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M315" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15847,6 +21543,26 @@
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L316" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M316" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15897,6 +21613,26 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L317" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M317" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15947,6 +21683,26 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L318" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M318" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15997,6 +21753,26 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M319" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16047,6 +21823,26 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M320" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N320" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16097,6 +21893,26 @@
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M321" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N321" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16147,6 +21963,26 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L322" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M322" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N322" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16197,6 +22033,26 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M323" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N323" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16247,6 +22103,26 @@
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M324" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N324" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16297,6 +22173,26 @@
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M325" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N325" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16347,6 +22243,26 @@
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M326" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N326" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16397,6 +22313,26 @@
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L327" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M327" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N327" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16447,6 +22383,26 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L328" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M328" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N328" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16497,6 +22453,26 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L329" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M329" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16547,6 +22523,26 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L330" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M330" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N330" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16597,6 +22593,26 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L331" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M331" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N331" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16647,6 +22663,26 @@
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L332" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M332" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16697,6 +22733,26 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M333" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16747,13 +22803,33 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L334" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M334" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -17413,7 +23489,7 @@
           <t>B | 1276呎 (3房)
 $3228万
 $25,300/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -17519,7 +23595,7 @@
           <t>A | 1625呎 (4+房)
 $5165万
 $31,782/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -17551,7 +23627,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -17583,7 +23659,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17591,7 +23667,7 @@
           <t>B | 1226呎 (3房)
 $2789万
 $22,745/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -17599,7 +23675,7 @@
           <t>C | 1304呎 (3房)
 $2875万
 $22,050/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -17615,7 +23691,7 @@
           <t>A | 1625呎 (4+房)
 $4791万
 $29,482/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -17647,7 +23723,7 @@
           <t>A | 1711呎 (4+房)
 $4600万
 $26,885/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -17655,7 +23731,7 @@
           <t>B | 1226呎 (3房)
 $3061万
 $24,969/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -17663,7 +23739,7 @@
           <t>C | 1254呎 (3房)
 $2960万
 $23,605/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -17679,7 +23755,7 @@
           <t>A | 945呎 (3房)
 $2145万
 $22,700/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -17687,7 +23763,7 @@
           <t>B | 1226呎 (3房)
 $3015万
 $24,594/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -17695,7 +23771,7 @@
           <t>C | 1252呎 (3房)
 $2591万
 $20,695/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -17703,7 +23779,7 @@
           <t>D | 724呎 (2房)
 $1643万
 $22,700/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -17718,7 +23794,7 @@
           <t>A | 945呎 (3房)
 $2060万
 $21,800/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -17726,7 +23802,7 @@
           <t>B | 1226呎 (3房)
 $2942万
 $24,000/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -17742,7 +23818,7 @@
           <t>D | 724呎 (2房)
 $1578万
 $21,800/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -17757,7 +23833,7 @@
           <t>A | 945呎 (3房)
 $1975万
 $20,900/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -17765,7 +23841,7 @@
           <t>B | 1226呎 (3房)
 $2897万
 $23,626/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -17781,7 +23857,7 @@
           <t>D | 724呎 (2房)
 $1513万
 $20,900/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -17796,7 +23872,7 @@
           <t>A | 945呎 (3房)
 $1909万
 $20,200/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -17804,7 +23880,7 @@
           <t>B | 1226呎 (3房)
 $2475万
 $20,191/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -17812,7 +23888,7 @@
           <t>C | 1252呎 (3房)
 $2708万
 $21,631/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -17820,7 +23896,7 @@
           <t>D | 724呎 (2房)
 $1548万
 $21,380/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -17835,7 +23911,7 @@
           <t>A | 945呎 (3房)
 $1843万
 $19,500/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -17843,7 +23919,7 @@
           <t>B | 1226呎 (3房)
 $2419万
 $19,733/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -17851,7 +23927,7 @@
           <t>C | 1252呎 (3房)
 $2331万
 $18,615/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -17859,7 +23935,7 @@
           <t>D | 724呎 (2房)
 $1419万
 $19,600/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -17874,7 +23950,7 @@
           <t>A | 945呎 (3房)
 $1777万
 $18,800/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -17882,7 +23958,7 @@
           <t>B | 1226呎 (3房)
 $2348万
 $19,150/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -17890,7 +23966,7 @@
           <t>C | 1252呎 (3房)
 $2292万
 $18,303/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -17898,7 +23974,7 @@
           <t>D | 724呎 (2房)
 $1361万
 $18,800/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -17913,7 +23989,7 @@
           <t>A | 945呎 (3房)
 $1692万
 $17,900/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -17921,7 +23997,7 @@
           <t>B | 1226呎 (3房)
 $2549万
 $20,789/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -17929,7 +24005,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -17937,7 +24013,7 @@
           <t>D | 724呎 (2房)
 $1300万
 $17,950/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -17952,7 +24028,7 @@
           <t>A | 945呎 (3房)
 $1635万
 $17,300/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -17960,7 +24036,7 @@
           <t>B | 1226呎 (3房)
 $2463万
 $20,087/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -17968,7 +24044,7 @@
           <t>C | 1252呎 (3房)
 $2213万
 $17,679/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -17976,7 +24052,7 @@
           <t>D | 724呎 (2房)
 $1281万
 $17,700/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -17991,7 +24067,7 @@
           <t>A | 945呎 (3房)
 $1577万
 $16,688/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -17999,7 +24075,7 @@
           <t>B | 1226呎 (3房)
 $2450万
 $19,983/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -18007,7 +24083,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -18015,7 +24091,7 @@
           <t>D | 724呎 (2房)
 $1339万
 $18,499/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -18030,7 +24106,7 @@
           <t>A | 1532呎 (4+房)
 $3964万
 $25,873/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -18038,7 +24114,7 @@
           <t>B | 1210呎 (3房)
 $2884万
 $23,836/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -18046,7 +24122,7 @@
           <t>C | 1254呎 (3房)
 $2478万
 $19,758/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -19143,7 +25219,7 @@
           <t>F | 768呎 (3房)
 $1821万
 $23,715/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -19155,10 +25231,10 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1865呎 (4+房)
+          <t>A | 1788呎 (4+房)
 $6600万
-$35,389/呎
-(26年-06月)</t>
+$36,913/呎
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -19184,7 +25260,7 @@
           <t>F | 769呎 (3房)
 $1803万
 $23,450/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -19199,7 +25275,7 @@
           <t>A | 1788呎 (4+房)
 $6900万
 $38,593/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -19225,7 +25301,7 @@
           <t>F | 769呎 (3房)
 $1785万
 $23,217/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -19240,7 +25316,7 @@
           <t>A | 1788呎 (4+房)
 $5908万
 $33,044/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19266,7 +25342,7 @@
           <t>F | 769呎 (3房)
 $1682万
 $21,872/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -19281,7 +25357,7 @@
           <t>A | 1788呎 (4+房)
 $6051万
 $33,841/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -19307,7 +25383,7 @@
           <t>F | 769呎 (3房)
 $1628万
 $21,172/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -19322,7 +25398,7 @@
           <t>A | 1788呎 (4+房)
 $5456万
 $30,514/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -19348,7 +25424,7 @@
           <t>F | 769呎 (3房)
 $1574万
 $20,473/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -19363,7 +25439,7 @@
           <t>A | 985呎 (3房)
 $2289万
 $23,239/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19371,7 +25447,7 @@
           <t>B | 725呎 (2房)
 $1579万
 $21,775/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -19379,7 +25455,7 @@
           <t>C | 961呎 (3房)
 $2704万
 $28,133/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -19403,7 +25479,7 @@
           <t>F | 769呎 (3房)
 $1528万
 $19,874/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -19418,7 +25494,7 @@
           <t>A | 985呎 (3房)
 $2090万
 $21,216/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19426,7 +25502,7 @@
           <t>B | 725呎 (2房)
 $1548万
 $21,348/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -19458,7 +25534,7 @@
           <t>F | 769呎 (3房)
 $1490万
 $19,375/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -19473,7 +25549,7 @@
           <t>A | 985呎 (3房)
 $2009万
 $20,400/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -19481,7 +25557,7 @@
           <t>B | 725呎 (2房)
 $1517万
 $20,929/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
@@ -19513,7 +25589,7 @@
           <t>F | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -19528,7 +25604,7 @@
           <t>A | 985呎 (3房)
 $1931万
 $19,600/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -19536,7 +25612,7 @@
           <t>B | 725呎 (2房)
 $1467万
 $20,228/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
@@ -19568,7 +25644,7 @@
           <t>F | 769呎 (3房)
 $1448万
 $18,828/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -19583,7 +25659,7 @@
           <t>A | 985呎 (3房)
 $1862万
 $18,900/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19591,7 +25667,7 @@
           <t>B | 727呎 (2房)
 $1423万
 $19,573/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -19610,7 +25686,7 @@
           <t>A | 985呎 (3房)
 $1807万
 $18,350/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -19618,7 +25694,7 @@
           <t>B | 729呎 (2房)
 $1383万
 $18,974/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -19637,7 +25713,7 @@
           <t>A | 985呎 (3房)
 $1753万
 $17,800/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19645,7 +25721,7 @@
           <t>B | 729呎 (2房)
 $1416万
 $19,417/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -19664,7 +25740,7 @@
           <t>A | 985呎 (3房)
 $1714万
 $17,400/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19672,7 +25748,7 @@
           <t>B | 729呎 (2房)
 $1281万
 $17,576/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>
@@ -19691,7 +25767,7 @@
           <t>A | 985呎 (3房)
 $1684万
 $17,100/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19699,7 +25775,7 @@
           <t>B | 729呎 (2房)
 $1252万
 $17,176/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>
@@ -19718,7 +25794,7 @@
           <t>A | 1640呎 (3房)
 $4380万
 $26,707/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr"/>
@@ -19877,7 +25953,7 @@
           <t>C | 769呎 (3房)
 $1586万
 $20,623/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -19885,7 +25961,7 @@
           <t>D | 712呎 (2房)
 $1504万
 $21,126/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -19916,7 +25992,7 @@
           <t>C | 769呎 (3房)
 $1563万
 $20,324/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -19924,7 +26000,7 @@
           <t>D | 712呎 (2房)
 $1478万
 $20,758/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -19955,7 +26031,7 @@
           <t>C | 769呎 (3房)
 $1540万
 $20,024/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -19963,7 +26039,7 @@
           <t>D | 712呎 (2房)
 $1452万
 $20,390/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -19994,7 +26070,7 @@
           <t>C | 769呎 (3房)
 $1517万
 $19,724/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -20002,7 +26078,7 @@
           <t>D | 712呎 (2房)
 $1356万
 $19,050/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -20033,7 +26109,7 @@
           <t>C | 769呎 (3房)
 $1494万
 $19,425/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -20041,7 +26117,7 @@
           <t>D | 712呎 (2房)
 $1339万
 $18,800/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -20056,7 +26132,7 @@
           <t>A | 1498呎 (4+房)
 $3810万
 $25,432/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20072,7 +26148,7 @@
           <t>C | 769呎 (3房)
 $1471万
 $19,125/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -20080,7 +26156,7 @@
           <t>D | 712呎 (2房)
 $1321万
 $18,550/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -20111,7 +26187,7 @@
           <t>C | 769呎 (3房)
 $1452万
 $18,875/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -20119,7 +26195,7 @@
           <t>D | 712呎 (2房)
 $1296万
 $18,200/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -20150,7 +26226,7 @@
           <t>C | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -20158,7 +26234,7 @@
           <t>D | 712呎 (2房)
 $1278万
 $17,950/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -20173,7 +26249,7 @@
           <t>A | 1555呎 (4+房)
 $3703万
 $23,814/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20189,7 +26265,7 @@
           <t>C | 769呎 (3房)
 $1398万
 $18,176/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -20197,7 +26273,7 @@
           <t>D | 712呎 (2房)
 $1257万
 $17,650/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -20212,7 +26288,7 @@
           <t>A | 1498呎 (4+房)
 $3370万
 $22,497/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20228,7 +26304,7 @@
           <t>C | 769呎 (3房)
 $1379万
 $17,927/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -20236,7 +26312,7 @@
           <t>D | 712呎 (2房)
 $1242万
 $17,450/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -20251,7 +26327,7 @@
           <t>A | 1498呎 (4+房)
 $3314万
 $22,121/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20267,7 +26343,7 @@
           <t>C | 768呎 (3房)
 $1432万
 $18,642/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -20275,7 +26351,7 @@
           <t>D | 712呎 (2房)
 $1228万
 $17,250/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -20290,7 +26366,7 @@
           <t>A | 1498呎 (4+房)
 $3234万
 $21,591/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -20298,7 +26374,7 @@
           <t>B | 1473呎 (4+房)
 $3244万
 $22,020/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20306,7 +26382,7 @@
           <t>C | 769呎 (3房)
 $1340万
 $17,427/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20314,7 +26390,7 @@
           <t>D | 712呎 (2房)
 $1214万
 $17,050/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -20329,7 +26405,7 @@
           <t>A | 1498呎 (4+房)
 $3380万
 $22,562/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20337,7 +26413,7 @@
           <t>B | 1473呎 (4+房)
 $3583万
 $24,327/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20345,7 +26421,7 @@
           <t>C | 769呎 (3房)
 $1321万
 $17,178/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20353,7 +26429,7 @@
           <t>D | 712呎 (2房)
 $1200万
 $16,850/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -20368,7 +26444,7 @@
           <t>A | 1498呎 (4+房)
 $3140万
 $20,960/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20384,7 +26460,7 @@
           <t>C | 769呎 (3房)
 $1297万
 $16,866/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20392,7 +26468,7 @@
           <t>D | 712呎 (2房)
 $1139万
 $15,998/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -20407,7 +26483,7 @@
           <t>A | 1498呎 (4+房)
 $3079万
 $20,553/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20415,7 +26491,7 @@
           <t>B | 1478呎 (4+房)
 $3343万
 $22,621/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -20432,7 +26508,7 @@
           <t>A | 1498呎 (4+房)
 $3110万
 $20,761/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20440,7 +26516,7 @@
           <t>B | 1478呎 (4+房)
 $2993万
 $20,252/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -20457,7 +26533,7 @@
           <t>A | 1498呎 (4+房)
 $3063万
 $20,450/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -20482,7 +26558,7 @@
           <t>A | 1498呎 (4+房)
 $3126万
 $20,865/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20490,7 +26566,7 @@
           <t>B | 1488呎 (4+房)
 $2930万
 $19,691/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -23480,11 +23480,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23492,7 +23510,7 @@
 (25年-05月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23500,24 +23518,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24278,44 +24278,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25090,14 +25090,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25105,7 +25132,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25113,33 +25140,6 @@
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -23480,29 +23480,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23510,7 +23492,7 @@
 (25年-05月-19日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23518,6 +23500,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24278,44 +24278,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25090,41 +25090,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25132,7 +25105,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25140,6 +25113,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,12 +137,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
@@ -223,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -294,10 +288,7 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5195,7 +5186,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5443,7 +5434,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5453,12 +5444,12 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -5468,12 +5459,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -5483,7 +5474,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12524,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -12542,14 +12533,14 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
         <v>18213000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>23715</v>
+        <v>23684</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -12560,7 +12551,7 @@
         <v>18213000</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>23715</v>
+        <v>23684</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -23401,27 +23392,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -23480,11 +23471,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23492,7 +23501,7 @@
 (25年-05月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23500,24 +23509,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23810,7 +23801,7 @@
           <t>C | 1302呎 (3房)
 $3204万
 $24,609/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -23844,12 +23835,12 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 1302呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -24278,44 +24269,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25078,7 +25069,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1996万
@@ -25090,14 +25081,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25105,7 +25123,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25114,33 +25132,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25173,7 +25164,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1957万
@@ -25216,10 +25207,10 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>F | 768呎 (3房)
+          <t>F | 769呎 (3房)
 $1821万
-$23,715/呎
-(26年-06月-29日)</t>
+$23,684/呎
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25496,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2820万
@@ -25560,7 +25551,7 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2764万
@@ -25615,7 +25606,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2690万

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -23471,37 +23471,19 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
 $25,300/呎
-(25年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23509,6 +23491,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23586,7 +23586,7 @@
           <t>A | 1625呎 (4+房)
 $5165万
 $31,782/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -23618,7 +23618,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -23650,7 +23650,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -23658,7 +23658,7 @@
           <t>B | 1226呎 (3房)
 $2789万
 $22,745/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -23666,7 +23666,7 @@
           <t>C | 1304呎 (3房)
 $2875万
 $22,050/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -23682,7 +23682,7 @@
           <t>A | 1625呎 (4+房)
 $4791万
 $29,482/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -23714,7 +23714,7 @@
           <t>A | 1711呎 (4+房)
 $4600万
 $26,885/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -23722,7 +23722,7 @@
           <t>B | 1226呎 (3房)
 $3061万
 $24,969/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -23730,7 +23730,7 @@
           <t>C | 1254呎 (3房)
 $2960万
 $23,605/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -23746,7 +23746,7 @@
           <t>A | 945呎 (3房)
 $2145万
 $22,700/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -23754,7 +23754,7 @@
           <t>B | 1226呎 (3房)
 $3015万
 $24,594/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -23762,7 +23762,7 @@
           <t>C | 1252呎 (3房)
 $2591万
 $20,695/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -23770,7 +23770,7 @@
           <t>D | 724呎 (2房)
 $1643万
 $22,700/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -23785,7 +23785,7 @@
           <t>A | 945呎 (3房)
 $2060万
 $21,800/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -23793,7 +23793,7 @@
           <t>B | 1226呎 (3房)
 $2942万
 $24,000/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -23809,7 +23809,7 @@
           <t>D | 724呎 (2房)
 $1578万
 $21,800/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
           <t>A | 945呎 (3房)
 $1975万
 $20,900/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -23832,7 +23832,7 @@
           <t>B | 1226呎 (3房)
 $2897万
 $23,626/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -23848,7 +23848,7 @@
           <t>D | 724呎 (2房)
 $1513万
 $20,900/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -23863,7 +23863,7 @@
           <t>A | 945呎 (3房)
 $1909万
 $20,200/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>B | 1226呎 (3房)
 $2475万
 $20,191/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>C | 1252呎 (3房)
 $2708万
 $21,631/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -23887,7 +23887,7 @@
           <t>D | 724呎 (2房)
 $1548万
 $21,380/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
           <t>A | 945呎 (3房)
 $1843万
 $19,500/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -23910,7 +23910,7 @@
           <t>B | 1226呎 (3房)
 $2419万
 $19,733/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -23918,7 +23918,7 @@
           <t>C | 1252呎 (3房)
 $2331万
 $18,615/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -23926,7 +23926,7 @@
           <t>D | 724呎 (2房)
 $1419万
 $19,600/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -23941,7 +23941,7 @@
           <t>A | 945呎 (3房)
 $1777万
 $18,800/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -23949,7 +23949,7 @@
           <t>B | 1226呎 (3房)
 $2348万
 $19,150/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -23957,7 +23957,7 @@
           <t>C | 1252呎 (3房)
 $2292万
 $18,303/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -23965,7 +23965,7 @@
           <t>D | 724呎 (2房)
 $1361万
 $18,800/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -23980,7 +23980,7 @@
           <t>A | 945呎 (3房)
 $1692万
 $17,900/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -23988,7 +23988,7 @@
           <t>B | 1226呎 (3房)
 $2549万
 $20,789/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -23996,7 +23996,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -24004,7 +24004,7 @@
           <t>D | 724呎 (2房)
 $1300万
 $17,950/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
           <t>A | 945呎 (3房)
 $1635万
 $17,300/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -24027,7 +24027,7 @@
           <t>B | 1226呎 (3房)
 $2463万
 $20,087/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -24035,7 +24035,7 @@
           <t>C | 1252呎 (3房)
 $2213万
 $17,679/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -24043,7 +24043,7 @@
           <t>D | 724呎 (2房)
 $1281万
 $17,700/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -24058,7 +24058,7 @@
           <t>A | 945呎 (3房)
 $1577万
 $16,688/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -24066,7 +24066,7 @@
           <t>B | 1226呎 (3房)
 $2450万
 $19,983/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -24074,7 +24074,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -24082,7 +24082,7 @@
           <t>D | 724呎 (2房)
 $1339万
 $18,499/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -24097,7 +24097,7 @@
           <t>A | 1532呎 (4+房)
 $3964万
 $25,873/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -24105,7 +24105,7 @@
           <t>B | 1210呎 (3房)
 $2884万
 $23,836/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -24113,7 +24113,7 @@
           <t>C | 1254呎 (3房)
 $2478万
 $19,758/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -24269,44 +24269,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25081,41 +25081,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25123,7 +25096,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25132,6 +25105,33 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
           <t>F | 769呎 (3房)
 $1821万
 $23,684/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -25225,7 +25225,7 @@
           <t>A | 1788呎 (4+房)
 $6600万
 $36,913/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25251,7 +25251,7 @@
           <t>F | 769呎 (3房)
 $1803万
 $23,450/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -25266,7 +25266,7 @@
           <t>A | 1788呎 (4+房)
 $6900万
 $38,593/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -25292,7 +25292,7 @@
           <t>F | 769呎 (3房)
 $1785万
 $23,217/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25307,7 +25307,7 @@
           <t>A | 1788呎 (4+房)
 $5908万
 $33,044/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -25333,7 +25333,7 @@
           <t>F | 769呎 (3房)
 $1682万
 $21,872/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25348,7 @@
           <t>A | 1788呎 (4+房)
 $6051万
 $33,841/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -25374,7 +25374,7 @@
           <t>F | 769呎 (3房)
 $1628万
 $21,172/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25389,7 +25389,7 @@
           <t>A | 1788呎 (4+房)
 $5456万
 $30,514/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -25415,7 +25415,7 @@
           <t>F | 769呎 (3房)
 $1574万
 $20,473/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25430,7 @@
           <t>A | 985呎 (3房)
 $2289万
 $23,239/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25438,7 +25438,7 @@
           <t>B | 725呎 (2房)
 $1579万
 $21,775/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25446,7 +25446,7 @@
           <t>C | 961呎 (3房)
 $2704万
 $28,133/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -25470,7 +25470,7 @@
           <t>F | 769呎 (3房)
 $1528万
 $19,874/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -25485,7 +25485,7 @@
           <t>A | 985呎 (3房)
 $2090万
 $21,216/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25493,7 +25493,7 @@
           <t>B | 725呎 (2房)
 $1548万
 $21,348/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -25525,7 +25525,7 @@
           <t>F | 769呎 (3房)
 $1490万
 $19,375/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
           <t>A | 985呎 (3房)
 $2009万
 $20,400/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25548,7 +25548,7 @@
           <t>B | 725呎 (2房)
 $1517万
 $20,929/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -25580,7 +25580,7 @@
           <t>F | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
           <t>A | 985呎 (3房)
 $1931万
 $19,600/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25603,7 +25603,7 @@
           <t>B | 725呎 (2房)
 $1467万
 $20,228/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -25635,7 +25635,7 @@
           <t>F | 769呎 (3房)
 $1448万
 $18,828/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -25650,7 +25650,7 @@
           <t>A | 985呎 (3房)
 $1862万
 $18,900/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25658,7 +25658,7 @@
           <t>B | 727呎 (2房)
 $1423万
 $19,573/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -25677,7 +25677,7 @@
           <t>A | 985呎 (3房)
 $1807万
 $18,350/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25685,7 +25685,7 @@
           <t>B | 729呎 (2房)
 $1383万
 $18,974/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -25704,7 +25704,7 @@
           <t>A | 985呎 (3房)
 $1753万
 $17,800/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25712,7 +25712,7 @@
           <t>B | 729呎 (2房)
 $1416万
 $19,417/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -25731,7 +25731,7 @@
           <t>A | 985呎 (3房)
 $1714万
 $17,400/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>B | 729呎 (2房)
 $1281万
 $17,576/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>
@@ -25758,7 +25758,7 @@
           <t>A | 985呎 (3房)
 $1684万
 $17,100/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -25766,7 +25766,7 @@
           <t>B | 729呎 (2房)
 $1252万
 $17,176/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>
@@ -25785,7 +25785,7 @@
           <t>A | 1640呎 (3房)
 $4380万
 $26,707/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr"/>
@@ -25944,7 +25944,7 @@
           <t>C | 769呎 (3房)
 $1586万
 $20,623/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -25952,7 +25952,7 @@
           <t>D | 712呎 (2房)
 $1504万
 $21,126/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25983,7 +25983,7 @@
           <t>C | 769呎 (3房)
 $1563万
 $20,324/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -25991,7 +25991,7 @@
           <t>D | 712呎 (2房)
 $1478万
 $20,758/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
           <t>C | 769呎 (3房)
 $1540万
 $20,024/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>D | 712呎 (2房)
 $1452万
 $20,390/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26061,7 @@
           <t>C | 769呎 (3房)
 $1517万
 $19,724/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>D | 712呎 (2房)
 $1356万
 $19,050/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26100,7 +26100,7 @@
           <t>C | 769呎 (3房)
 $1494万
 $19,425/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26108,7 +26108,7 @@
           <t>D | 712呎 (2房)
 $1339万
 $18,800/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
           <t>A | 1498呎 (4+房)
 $3810万
 $25,432/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -26139,7 +26139,7 @@
           <t>C | 769呎 (3房)
 $1471万
 $19,125/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26147,7 +26147,7 @@
           <t>D | 712呎 (2房)
 $1321万
 $18,550/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -26178,7 +26178,7 @@
           <t>C | 769呎 (3房)
 $1452万
 $18,875/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26186,7 +26186,7 @@
           <t>D | 712呎 (2房)
 $1296万
 $18,200/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
           <t>C | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26225,7 +26225,7 @@
           <t>D | 712呎 (2房)
 $1278万
 $17,950/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
           <t>A | 1555呎 (4+房)
 $3703万
 $23,814/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -26256,7 +26256,7 @@
           <t>C | 769呎 (3房)
 $1398万
 $18,176/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -26264,7 +26264,7 @@
           <t>D | 712呎 (2房)
 $1257万
 $17,650/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
           <t>A | 1498呎 (4+房)
 $3370万
 $22,497/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -26295,7 +26295,7 @@
           <t>C | 769呎 (3房)
 $1379万
 $17,927/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26303,7 +26303,7 @@
           <t>D | 712呎 (2房)
 $1242万
 $17,450/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -26318,7 +26318,7 @@
           <t>A | 1498呎 (4+房)
 $3314万
 $22,121/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>C | 768呎 (3房)
 $1432万
 $18,642/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>D | 712呎 (2房)
 $1228万
 $17,250/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
           <t>A | 1498呎 (4+房)
 $3234万
 $21,591/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>B | 1473呎 (4+房)
 $3244万
 $22,020/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>C | 769呎 (3房)
 $1340万
 $17,427/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>D | 712呎 (2房)
 $1214万
 $17,050/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -26396,7 +26396,7 @@
           <t>A | 1498呎 (4+房)
 $3380万
 $22,562/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26404,7 +26404,7 @@
           <t>B | 1473呎 (4+房)
 $3583万
 $24,327/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26412,7 +26412,7 @@
           <t>C | 769呎 (3房)
 $1321万
 $17,178/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26420,7 +26420,7 @@
           <t>D | 712呎 (2房)
 $1200万
 $16,850/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
           <t>A | 1498呎 (4+房)
 $3140万
 $20,960/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -26451,7 +26451,7 @@
           <t>C | 769呎 (3房)
 $1297万
 $16,866/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26459,7 +26459,7 @@
           <t>D | 712呎 (2房)
 $1139万
 $15,998/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -26474,7 +26474,7 @@
           <t>A | 1498呎 (4+房)
 $3079万
 $20,553/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26482,7 +26482,7 @@
           <t>B | 1478呎 (4+房)
 $3343万
 $22,621/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -26499,7 +26499,7 @@
           <t>A | 1498呎 (4+房)
 $3110万
 $20,761/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>B | 1478呎 (4+房)
 $2993万
 $20,252/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -26524,7 +26524,7 @@
           <t>A | 1498呎 (4+房)
 $3063万
 $20,450/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -26549,7 +26549,7 @@
           <t>A | 1498呎 (4+房)
 $3126万
 $20,865/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26557,7 +26557,7 @@
           <t>B | 1488呎 (4+房)
 $2930万
 $19,691/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -23480,7 +23480,7 @@
           <t>B | 1276呎 (3房)
 $3228万
 $25,300/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -23586,7 +23586,7 @@
           <t>A | 1625呎 (4+房)
 $5165万
 $31,782/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -23618,7 +23618,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -23650,7 +23650,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -23658,7 +23658,7 @@
           <t>B | 1226呎 (3房)
 $2789万
 $22,745/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -23666,7 +23666,7 @@
           <t>C | 1304呎 (3房)
 $2875万
 $22,050/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -23682,7 +23682,7 @@
           <t>A | 1625呎 (4+房)
 $4791万
 $29,482/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -23714,7 +23714,7 @@
           <t>A | 1711呎 (4+房)
 $4600万
 $26,885/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -23722,7 +23722,7 @@
           <t>B | 1226呎 (3房)
 $3061万
 $24,969/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -23730,7 +23730,7 @@
           <t>C | 1254呎 (3房)
 $2960万
 $23,605/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -23746,7 +23746,7 @@
           <t>A | 945呎 (3房)
 $2145万
 $22,700/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -23754,7 +23754,7 @@
           <t>B | 1226呎 (3房)
 $3015万
 $24,594/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -23762,7 +23762,7 @@
           <t>C | 1252呎 (3房)
 $2591万
 $20,695/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -23770,7 +23770,7 @@
           <t>D | 724呎 (2房)
 $1643万
 $22,700/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -23785,7 +23785,7 @@
           <t>A | 945呎 (3房)
 $2060万
 $21,800/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -23793,7 +23793,7 @@
           <t>B | 1226呎 (3房)
 $2942万
 $24,000/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -23809,7 +23809,7 @@
           <t>D | 724呎 (2房)
 $1578万
 $21,800/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
           <t>A | 945呎 (3房)
 $1975万
 $20,900/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -23832,7 +23832,7 @@
           <t>B | 1226呎 (3房)
 $2897万
 $23,626/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -23848,7 +23848,7 @@
           <t>D | 724呎 (2房)
 $1513万
 $20,900/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -23863,7 +23863,7 @@
           <t>A | 945呎 (3房)
 $1909万
 $20,200/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>B | 1226呎 (3房)
 $2475万
 $20,191/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>C | 1252呎 (3房)
 $2708万
 $21,631/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -23887,7 +23887,7 @@
           <t>D | 724呎 (2房)
 $1548万
 $21,380/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
           <t>A | 945呎 (3房)
 $1843万
 $19,500/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -23910,7 +23910,7 @@
           <t>B | 1226呎 (3房)
 $2419万
 $19,733/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -23918,7 +23918,7 @@
           <t>C | 1252呎 (3房)
 $2331万
 $18,615/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -23926,7 +23926,7 @@
           <t>D | 724呎 (2房)
 $1419万
 $19,600/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -23941,7 +23941,7 @@
           <t>A | 945呎 (3房)
 $1777万
 $18,800/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -23949,7 +23949,7 @@
           <t>B | 1226呎 (3房)
 $2348万
 $19,150/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -23957,7 +23957,7 @@
           <t>C | 1252呎 (3房)
 $2292万
 $18,303/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -23965,7 +23965,7 @@
           <t>D | 724呎 (2房)
 $1361万
 $18,800/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -23980,7 +23980,7 @@
           <t>A | 945呎 (3房)
 $1692万
 $17,900/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -23988,7 +23988,7 @@
           <t>B | 1226呎 (3房)
 $2549万
 $20,789/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -23996,7 +23996,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -24004,7 +24004,7 @@
           <t>D | 724呎 (2房)
 $1300万
 $17,950/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
           <t>A | 945呎 (3房)
 $1635万
 $17,300/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -24027,7 +24027,7 @@
           <t>B | 1226呎 (3房)
 $2463万
 $20,087/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -24035,7 +24035,7 @@
           <t>C | 1252呎 (3房)
 $2213万
 $17,679/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -24043,7 +24043,7 @@
           <t>D | 724呎 (2房)
 $1281万
 $17,700/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -24058,7 +24058,7 @@
           <t>A | 945呎 (3房)
 $1577万
 $16,688/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -24066,7 +24066,7 @@
           <t>B | 1226呎 (3房)
 $2450万
 $19,983/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -24074,7 +24074,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -24082,7 +24082,7 @@
           <t>D | 724呎 (2房)
 $1339万
 $18,499/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -24097,7 +24097,7 @@
           <t>A | 1532呎 (4+房)
 $3964万
 $25,873/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -24105,7 +24105,7 @@
           <t>B | 1210呎 (3房)
 $2884万
 $23,836/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -24113,7 +24113,7 @@
           <t>C | 1254呎 (3房)
 $2478万
 $19,758/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -25210,7 +25210,7 @@
           <t>F | 769呎 (3房)
 $1821万
 $23,684/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -25225,7 +25225,7 @@
           <t>A | 1788呎 (4+房)
 $6600万
 $36,913/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25251,7 +25251,7 @@
           <t>F | 769呎 (3房)
 $1803万
 $23,450/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -25266,7 +25266,7 @@
           <t>A | 1788呎 (4+房)
 $6900万
 $38,593/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -25292,7 +25292,7 @@
           <t>F | 769呎 (3房)
 $1785万
 $23,217/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -25307,7 +25307,7 @@
           <t>A | 1788呎 (4+房)
 $5908万
 $33,044/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -25333,7 +25333,7 @@
           <t>F | 769呎 (3房)
 $1682万
 $21,872/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25348,7 @@
           <t>A | 1788呎 (4+房)
 $6051万
 $33,841/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -25374,7 +25374,7 @@
           <t>F | 769呎 (3房)
 $1628万
 $21,172/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -25389,7 +25389,7 @@
           <t>A | 1788呎 (4+房)
 $5456万
 $30,514/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -25415,7 +25415,7 @@
           <t>F | 769呎 (3房)
 $1574万
 $20,473/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25430,7 @@
           <t>A | 985呎 (3房)
 $2289万
 $23,239/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25438,7 +25438,7 @@
           <t>B | 725呎 (2房)
 $1579万
 $21,775/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25446,7 +25446,7 @@
           <t>C | 961呎 (3房)
 $2704万
 $28,133/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -25470,7 +25470,7 @@
           <t>F | 769呎 (3房)
 $1528万
 $19,874/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -25485,7 +25485,7 @@
           <t>A | 985呎 (3房)
 $2090万
 $21,216/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25493,7 +25493,7 @@
           <t>B | 725呎 (2房)
 $1548万
 $21,348/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -25525,7 +25525,7 @@
           <t>F | 769呎 (3房)
 $1490万
 $19,375/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
           <t>A | 985呎 (3房)
 $2009万
 $20,400/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25548,7 +25548,7 @@
           <t>B | 725呎 (2房)
 $1517万
 $20,929/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -25580,7 +25580,7 @@
           <t>F | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
           <t>A | 985呎 (3房)
 $1931万
 $19,600/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25603,7 +25603,7 @@
           <t>B | 725呎 (2房)
 $1467万
 $20,228/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -25635,7 +25635,7 @@
           <t>F | 769呎 (3房)
 $1448万
 $18,828/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -25650,7 +25650,7 @@
           <t>A | 985呎 (3房)
 $1862万
 $18,900/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25658,7 +25658,7 @@
           <t>B | 727呎 (2房)
 $1423万
 $19,573/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -25677,7 +25677,7 @@
           <t>A | 985呎 (3房)
 $1807万
 $18,350/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25685,7 +25685,7 @@
           <t>B | 729呎 (2房)
 $1383万
 $18,974/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -25704,7 +25704,7 @@
           <t>A | 985呎 (3房)
 $1753万
 $17,800/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25712,7 +25712,7 @@
           <t>B | 729呎 (2房)
 $1416万
 $19,417/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -25731,7 +25731,7 @@
           <t>A | 985呎 (3房)
 $1714万
 $17,400/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>B | 729呎 (2房)
 $1281万
 $17,576/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>
@@ -25758,7 +25758,7 @@
           <t>A | 985呎 (3房)
 $1684万
 $17,100/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -25766,7 +25766,7 @@
           <t>B | 729呎 (2房)
 $1252万
 $17,176/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>
@@ -25785,7 +25785,7 @@
           <t>A | 1640呎 (3房)
 $4380万
 $26,707/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr"/>
@@ -25944,7 +25944,7 @@
           <t>C | 769呎 (3房)
 $1586万
 $20,623/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -25952,7 +25952,7 @@
           <t>D | 712呎 (2房)
 $1504万
 $21,126/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -25983,7 +25983,7 @@
           <t>C | 769呎 (3房)
 $1563万
 $20,324/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -25991,7 +25991,7 @@
           <t>D | 712呎 (2房)
 $1478万
 $20,758/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
           <t>C | 769呎 (3房)
 $1540万
 $20,024/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>D | 712呎 (2房)
 $1452万
 $20,390/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26061,7 @@
           <t>C | 769呎 (3房)
 $1517万
 $19,724/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>D | 712呎 (2房)
 $1356万
 $19,050/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -26100,7 +26100,7 @@
           <t>C | 769呎 (3房)
 $1494万
 $19,425/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26108,7 +26108,7 @@
           <t>D | 712呎 (2房)
 $1339万
 $18,800/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
           <t>A | 1498呎 (4+房)
 $3810万
 $25,432/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -26139,7 +26139,7 @@
           <t>C | 769呎 (3房)
 $1471万
 $19,125/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26147,7 +26147,7 @@
           <t>D | 712呎 (2房)
 $1321万
 $18,550/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -26178,7 +26178,7 @@
           <t>C | 769呎 (3房)
 $1452万
 $18,875/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26186,7 +26186,7 @@
           <t>D | 712呎 (2房)
 $1296万
 $18,200/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
           <t>C | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26225,7 +26225,7 @@
           <t>D | 712呎 (2房)
 $1278万
 $17,950/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
           <t>A | 1555呎 (4+房)
 $3703万
 $23,814/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -26256,7 +26256,7 @@
           <t>C | 769呎 (3房)
 $1398万
 $18,176/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -26264,7 +26264,7 @@
           <t>D | 712呎 (2房)
 $1257万
 $17,650/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
           <t>A | 1498呎 (4+房)
 $3370万
 $22,497/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -26295,7 +26295,7 @@
           <t>C | 769呎 (3房)
 $1379万
 $17,927/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26303,7 +26303,7 @@
           <t>D | 712呎 (2房)
 $1242万
 $17,450/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -26318,7 +26318,7 @@
           <t>A | 1498呎 (4+房)
 $3314万
 $22,121/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>C | 768呎 (3房)
 $1432万
 $18,642/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>D | 712呎 (2房)
 $1228万
 $17,250/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
           <t>A | 1498呎 (4+房)
 $3234万
 $21,591/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>B | 1473呎 (4+房)
 $3244万
 $22,020/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>C | 769呎 (3房)
 $1340万
 $17,427/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>D | 712呎 (2房)
 $1214万
 $17,050/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -26396,7 +26396,7 @@
           <t>A | 1498呎 (4+房)
 $3380万
 $22,562/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26404,7 +26404,7 @@
           <t>B | 1473呎 (4+房)
 $3583万
 $24,327/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26412,7 +26412,7 @@
           <t>C | 769呎 (3房)
 $1321万
 $17,178/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26420,7 +26420,7 @@
           <t>D | 712呎 (2房)
 $1200万
 $16,850/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
           <t>A | 1498呎 (4+房)
 $3140万
 $20,960/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -26451,7 +26451,7 @@
           <t>C | 769呎 (3房)
 $1297万
 $16,866/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26459,7 +26459,7 @@
           <t>D | 712呎 (2房)
 $1139万
 $15,998/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -26474,7 +26474,7 @@
           <t>A | 1498呎 (4+房)
 $3079万
 $20,553/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26482,7 +26482,7 @@
           <t>B | 1478呎 (4+房)
 $3343万
 $22,621/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -26499,7 +26499,7 @@
           <t>A | 1498呎 (4+房)
 $3110万
 $20,761/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>B | 1478呎 (4+房)
 $2993万
 $20,252/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -26524,7 +26524,7 @@
           <t>A | 1498呎 (4+房)
 $3063万
 $20,450/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -26549,7 +26549,7 @@
           <t>A | 1498呎 (4+房)
 $3126万
 $20,865/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26557,7 +26557,7 @@
           <t>B | 1488呎 (4+房)
 $2930万
 $19,691/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>
@@ -26718,34 +26718,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
+++ b/files/九龙-石硖尾-Beacon Peak 第1期.xlsx
@@ -5434,38 +5434,30 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>29659560</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>22780</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K72" s="5" t="n">
+        <v>29659560</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>22780</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5474,7 +5466,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23392,7 +23384,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23402,7 +23394,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23835,12 +23827,12 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 1302呎 (3房)
-招标单位
--
-(在售)</t>
+$2966万
+$22,780/呎
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
